--- a/pfmea_ai/NEW_PFMEA__merge_mode_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__merge_mode_gpt4omini.xlsx
@@ -2408,7 +2408,7 @@
       <c r="AS17" s="208" t="n"/>
       <c r="AT17" s="208" t="n"/>
     </row>
-    <row r="18" ht="102" customFormat="1" customHeight="1" s="8">
+    <row r="18" ht="142.5" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
         <is>
           <t>HEAD LAMP STAGE</t>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="118.5" customFormat="1" customHeight="1" s="13">
+    <row r="29" ht="240" customFormat="1" customHeight="1" s="13">
       <c r="B29" s="210" t="n"/>
       <c r="C29" s="211" t="n"/>
       <c r="D29" s="210" t="n"/>

--- a/pfmea_ai/NEW_PFMEA__merge_mode_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__merge_mode_gpt4omini.xlsx
@@ -1611,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT29"/>
+  <dimension ref="A1:AV29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.85546875" customWidth="1" min="1" max="1"/>
@@ -1624,6 +1624,8 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="45" customWidth="1" min="45" max="45"/>
     <col width="50" customWidth="1" min="46" max="46"/>
+    <col width="45" customWidth="1" min="47" max="47"/>
+    <col width="35" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="1">
@@ -2066,6 +2068,8 @@
       <c r="AR13" s="205" t="n"/>
       <c r="AS13" s="205" t="n"/>
       <c r="AT13" s="205" t="n"/>
+      <c r="AU13" s="205" t="n"/>
+      <c r="AV13" s="205" t="n"/>
     </row>
     <row r="14" ht="22.5" customFormat="1" customHeight="1" s="1">
       <c r="A14" s="198" t="n"/>
@@ -2114,6 +2118,8 @@
       <c r="AR14" s="205" t="n"/>
       <c r="AS14" s="205" t="n"/>
       <c r="AT14" s="205" t="n"/>
+      <c r="AU14" s="205" t="n"/>
+      <c r="AV14" s="205" t="n"/>
     </row>
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
@@ -2309,6 +2315,16 @@
       <c r="AT15" s="208" t="inlineStr">
         <is>
           <t>Remark</t>
+        </is>
+      </c>
+      <c r="AU15" s="208" t="inlineStr">
+        <is>
+          <t>AI Review</t>
+        </is>
+      </c>
+      <c r="AV15" s="208" t="inlineStr">
+        <is>
+          <t>Manual Review</t>
         </is>
       </c>
     </row>
@@ -2359,6 +2375,8 @@
       <c r="AR16" s="208" t="n"/>
       <c r="AS16" s="208" t="n"/>
       <c r="AT16" s="208" t="n"/>
+      <c r="AU16" s="208" t="n"/>
+      <c r="AV16" s="208" t="n"/>
     </row>
     <row r="17" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="198" t="n"/>
@@ -2407,6 +2425,8 @@
       <c r="AR17" s="208" t="n"/>
       <c r="AS17" s="208" t="n"/>
       <c r="AT17" s="208" t="n"/>
+      <c r="AU17" s="208" t="n"/>
+      <c r="AV17" s="208" t="n"/>
     </row>
     <row r="18" ht="142.5" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="120" t="inlineStr">
@@ -2575,6 +2595,8 @@
 ( NOT AS PER MODEL). Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AU18" s="223" t="inlineStr"/>
+      <c r="AV18" s="223" t="inlineStr"/>
     </row>
     <row r="19" ht="207" customFormat="1" customHeight="1" s="8">
       <c r="B19" s="210" t="n"/>
@@ -2627,6 +2649,8 @@
       <c r="AR19" s="223" t="n"/>
       <c r="AS19" s="223" t="n"/>
       <c r="AT19" s="223" t="n"/>
+      <c r="AU19" s="223" t="n"/>
+      <c r="AV19" s="223" t="n"/>
     </row>
     <row r="20" ht="117" customFormat="1" customHeight="1" s="8">
       <c r="B20" s="210" t="n"/>
@@ -2713,6 +2737,8 @@
 - Same Failure Cause text is also used, verbatim, on a different Failure Mode: SCRATCH / DAMAGE ON HEAD LAMP. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AU20" s="223" t="inlineStr"/>
+      <c r="AV20" s="223" t="inlineStr"/>
     </row>
     <row r="21" ht="153" customFormat="1" customHeight="1" s="8">
       <c r="B21" s="210" t="n"/>
@@ -2765,6 +2791,8 @@
       <c r="AR21" s="223" t="n"/>
       <c r="AS21" s="223" t="n"/>
       <c r="AT21" s="223" t="n"/>
+      <c r="AU21" s="223" t="n"/>
+      <c r="AV21" s="223" t="n"/>
     </row>
     <row r="22" ht="119.25" customFormat="1" customHeight="1" s="8">
       <c r="B22" s="210" t="n"/>
@@ -2855,6 +2883,8 @@
           <t>- AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
       </c>
+      <c r="AU22" s="223" t="inlineStr"/>
+      <c r="AV22" s="223" t="inlineStr"/>
     </row>
     <row r="23" ht="186.95" customFormat="1" customHeight="1" s="14">
       <c r="B23" s="210" t="n"/>
@@ -2927,6 +2957,8 @@
       <c r="AR23" s="223" t="n"/>
       <c r="AS23" s="223" t="n"/>
       <c r="AT23" s="223" t="n"/>
+      <c r="AU23" s="223" t="n"/>
+      <c r="AV23" s="223" t="n"/>
     </row>
     <row r="24" ht="130.5" customFormat="1" customHeight="1" s="14">
       <c r="B24" s="210" t="n"/>
@@ -3006,6 +3038,8 @@
           <t>- AI severity (10) differs from plant-recorded (5) - review recommended.</t>
         </is>
       </c>
+      <c r="AU24" s="223" t="inlineStr"/>
+      <c r="AV24" s="223" t="inlineStr"/>
     </row>
     <row r="25" ht="130.5" customFormat="1" customHeight="1" s="14">
       <c r="B25" s="210" t="n"/>
@@ -3062,6 +3096,8 @@
       <c r="AR25" s="223" t="n"/>
       <c r="AS25" s="223" t="n"/>
       <c r="AT25" s="223" t="n"/>
+      <c r="AU25" s="223" t="n"/>
+      <c r="AV25" s="223" t="n"/>
     </row>
     <row r="26" ht="135" customFormat="1" customHeight="1" s="14">
       <c r="B26" s="210" t="n"/>
@@ -3163,6 +3199,8 @@
           <t>- Merged failure mode (2 distinct modes detected) - see the A/B breakdown in Severity/Detection/Prevention above, matched against the Failure Mode text.</t>
         </is>
       </c>
+      <c r="AU26" s="223" t="inlineStr"/>
+      <c r="AV26" s="223" t="inlineStr"/>
     </row>
     <row r="27" ht="156" customFormat="1" customHeight="1" s="13">
       <c r="B27" s="210" t="n"/>
@@ -3225,6 +3263,8 @@
       <c r="AR27" s="223" t="n"/>
       <c r="AS27" s="223" t="n"/>
       <c r="AT27" s="223" t="n"/>
+      <c r="AU27" s="223" t="n"/>
+      <c r="AV27" s="223" t="n"/>
     </row>
     <row r="28" ht="151.5" customFormat="1" customHeight="1" s="13">
       <c r="B28" s="210" t="n"/>
@@ -3317,6 +3357,8 @@
           <t>- Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED - OVER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AU28" s="223" t="inlineStr"/>
+      <c r="AV28" s="223" t="inlineStr"/>
     </row>
     <row r="29" ht="240" customFormat="1" customHeight="1" s="13">
       <c r="B29" s="210" t="n"/>
@@ -3399,10 +3441,12 @@
 - Same Failure Cause text is also used, verbatim, on a different Failure Mode: TORQUE NOT ACHIEVED-UNDER TORQUE. Verify this Cause actually belongs to this row and wasn't copy-pasted.</t>
         </is>
       </c>
+      <c r="AU29" s="223" t="inlineStr"/>
+      <c r="AV29" s="223" t="inlineStr"/>
     </row>
     <row r="30" customFormat="1" s="18"/>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="181">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="K18:L29"/>
     <mergeCell ref="I24:J25"/>
@@ -3410,6 +3454,7 @@
     <mergeCell ref="AM15:AM17"/>
     <mergeCell ref="AT18:AT19"/>
     <mergeCell ref="AE15:AE17"/>
+    <mergeCell ref="AV18:AV19"/>
     <mergeCell ref="AG15:AG17"/>
     <mergeCell ref="C15:D17"/>
     <mergeCell ref="K10:T10"/>
@@ -3420,18 +3465,20 @@
     <mergeCell ref="T13:AA14"/>
     <mergeCell ref="S1:T2"/>
     <mergeCell ref="D12:F12"/>
+    <mergeCell ref="AU24:AU25"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G13:L14"/>
     <mergeCell ref="AR24:AR25"/>
     <mergeCell ref="K9:T9"/>
     <mergeCell ref="K5:T5"/>
     <mergeCell ref="T28:U29"/>
+    <mergeCell ref="AU26:AU27"/>
     <mergeCell ref="AN15:AN17"/>
     <mergeCell ref="AT26:AT27"/>
     <mergeCell ref="K11:T11"/>
     <mergeCell ref="I3:T4"/>
     <mergeCell ref="AS18:AS19"/>
-    <mergeCell ref="AM13:AT14"/>
+    <mergeCell ref="AU18:AU19"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="AM22:AM23"/>
     <mergeCell ref="K12:T12"/>
@@ -3451,7 +3498,9 @@
     <mergeCell ref="AQ20:AQ21"/>
     <mergeCell ref="T15:U17"/>
     <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AM13:AV14"/>
     <mergeCell ref="AT15:AT17"/>
+    <mergeCell ref="AV15:AV17"/>
     <mergeCell ref="K7:T7"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="A12:C12"/>
@@ -3485,6 +3534,7 @@
     <mergeCell ref="AC15:AC17"/>
     <mergeCell ref="R28:S29"/>
     <mergeCell ref="I26:J27"/>
+    <mergeCell ref="AV20:AV21"/>
     <mergeCell ref="AQ24:AQ25"/>
     <mergeCell ref="AS24:AS25"/>
     <mergeCell ref="AD15:AD17"/>
@@ -3496,6 +3546,8 @@
     <mergeCell ref="I28:J29"/>
     <mergeCell ref="AF15:AF17"/>
     <mergeCell ref="AS20:AS21"/>
+    <mergeCell ref="AU20:AU21"/>
+    <mergeCell ref="AV22:AV23"/>
     <mergeCell ref="AQ26:AQ27"/>
     <mergeCell ref="AS26:AS27"/>
     <mergeCell ref="P15:Q17"/>
@@ -3517,13 +3569,16 @@
     <mergeCell ref="AM20:AM21"/>
     <mergeCell ref="W28:X29"/>
     <mergeCell ref="P20:Q21"/>
+    <mergeCell ref="AV24:AV25"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="AO22:AO23"/>
     <mergeCell ref="P22:Q23"/>
     <mergeCell ref="AR22:AR23"/>
     <mergeCell ref="V18:V21"/>
     <mergeCell ref="AT22:AT23"/>
+    <mergeCell ref="AV26:AV27"/>
     <mergeCell ref="T19:U19"/>
+    <mergeCell ref="AU15:AU17"/>
     <mergeCell ref="AO15:AO17"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="V27:V29"/>
@@ -3569,6 +3624,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="T23:U23"/>
     <mergeCell ref="D10:F10"/>
+    <mergeCell ref="AU22:AU23"/>
     <mergeCell ref="AR26:AR27"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="T18:U18"/>

--- a/pfmea_ai/NEW_PFMEA__merge_mode_gpt4omini.xlsx
+++ b/pfmea_ai/NEW_PFMEA__merge_mode_gpt4omini.xlsx
@@ -2124,9 +2124,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -2145,8 +2167,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -2437,36 +2481,293 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 RH / LH HEAD LAMP FITMENT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool, Traceability scanner
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Connections, Bolt fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 Headlamp assembly in specific design (bulb/LED assembly, lens fitting, aiming, electrical connection)
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Provide adequate illumination of the road ahead during low-light or night conditions
 2. Ensure visibility of the vehicle to other road users
 3. Meet legal/regulatory lighting requirements (beam pattern, intensity, color)</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -2478,32 +2779,185 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. COLLECT THE HEAD LAMP LH / RH SIDE FROM STORAGE AREA AND SCAN THE PART
 2. CONNECT THE 2 CONNECTORS WITH HEAD LAMP
 3. ALIGN THE HEAD LAMP WITH THE BIW AND THEN TIGHT WITH BOLTS
-2. Machine:
-Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Install Head lamp from sequencing trolley and scan
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Install Head lamp from sequencing trolley and scan
 2. Align H/L with BIW, then do the connections with wiring harness with head lamp and tight with bolts
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong Head lamp variant installed
 2. FURTHER OPERATION NOT POSSIBLE
 3. Lens cracked or broken
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Headlamp does not turn ON
 2. Insufficient brightness / dim light
 3. Customer dissatisfaction</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -2812,16 +3266,82 @@
       <c r="L22" s="210" t="n"/>
       <c r="M22" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wiring harness partially connected (loose fitment)
 2. Electrical connector loose or damaged
 3. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Incorrect beam alignment
 2. Headlamp does not turn ON
 3. Reduced road visibility
 4. Increased risk of accident</t>
+          </r>
         </is>
       </c>
       <c r="N22" s="207" t="n"/>
@@ -3117,16 +3637,103 @@
       <c r="L26" s="210" t="n"/>
       <c r="M26" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting screws under-torqued or over-torqued
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Lens cracked or broken
 2. LED / BULB burnout
 3. Water ingress inside lamp
 4. Rattling or vibration noise during driving
 5. Driver discomfort or eye strain</t>
+          </r>
         </is>
       </c>
       <c r="N26" s="207" t="n"/>
@@ -4120,9 +4727,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -4141,8 +4770,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -4363,37 +5014,294 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 FRONT GRILL FITMENT- HIGH VARIANT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool, Traceability scanner
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Connections, 
 Bolts &amp; pushpin   fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 To correctly install front grill fitment as per BIW design specifications.
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Allow airflow to the radiator, condenser, and engine compartment
 2. Protect cooling components from debris, stones, insects
 3. Provide vehicle styling and brand identity</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -4405,33 +5313,186 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. TAKE THE FRONT GRILL FROM THE STORAGE AREA AND SCAN THE PART
 2. CONNECT THE CONNECTORS WITH GRILL
 3. INSERT &amp; 
 ALIGN THE FRONT GRILL WITH BIW AND THEN TIGHT WITH BOLTS AND PUSHPINS
-2. Machine:
-Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Install Front grill from sequencing trolley and scan
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Install Front grill from sequencing trolley and scan
 2. Then do the connections with wiring harness with grill and align with BIW and tight with bolts &amp; pushpins
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong front grill variant installed
 2. FURTHER OPERATION NOT POSSIBLE
 3. Gaps or scratches on grill 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Incorrect distance / object detection
 2. Water/dust ingress affecting sensor
 3. Customer dissatisfaction</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -4629,16 +5690,82 @@
       <c r="L22" s="210" t="n"/>
       <c r="M22" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wiring harness partially connected (loose fitment)
 2. Wiring harness pinched or damaged
 3. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. False ADAS warnings or alerts
 2. Incorrect object detection
 3. Lane assist / collision warning inoperative
 4. Increased risk of accident</t>
+          </r>
         </is>
       </c>
       <c r="N22" s="207" t="n"/>
@@ -4845,16 +5972,103 @@
       <c r="L26" s="210" t="n"/>
       <c r="M26" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting bolts under-torqued or over-torqued
 3. Broken clips
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Customer loss of confidence in vehicle safety
 2. False collision warnings provided to driver
 3. Water/dust ingress affecting sensor
 4. Rattling or vibration noise during driving</t>
+          </r>
         </is>
       </c>
       <c r="N26" s="207" t="n"/>
@@ -5656,9 +6870,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -5677,8 +6913,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -5899,36 +7157,293 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 FRONT GRILL FITMENT- LOW VARIANT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool, Traceability scanner
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Bolts &amp; pushpin   fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 To correctly install front grill fitment as per BIW design specifications.
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Allow airflow to the radiator, condenser, and engine compartment
 2. Protect cooling components from debris, stones, insects
 3. Provide vehicle styling and brand identity</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -5940,32 +7455,185 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. TAKE THE FRONT GRILL FROM THE STORAGE AREA AND SCAN THE PART
 2. INSERT &amp; 
 ALIGN THE FRONT GRILL WITH BIW AND THEN TIGHT WITH BOLTS AND PUSHPINS
-2. Machine:
-Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 4NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Install Front grill from sequencing trolley and scan
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Install Front grill from sequencing trolley and scan
 2. Align with BIW and tight with bolts &amp; pushpins
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong front grill variant installed
 2. FURTHER OPERATION NOT POSSIBLE
 3. Gaps or scratches on grill 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Water/dust ingress affecting sensor
 2. Customer dissatisfaction
 3. Bad appereance of vehicle</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -6126,11 +7794,77 @@
       <c r="L21" s="210" t="n"/>
       <c r="M21" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Water/dust ingress affecting part warrenty</t>
+          </r>
         </is>
       </c>
       <c r="N21" s="207" t="n"/>
@@ -6306,14 +8040,101 @@
       <c r="L24" s="210" t="n"/>
       <c r="M24" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting bolts under-torqued or over-torqued
 3. Broken clips
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Water/dust ingress affecting sensor
 2. Rattling or vibration noise during driving</t>
+          </r>
         </is>
       </c>
       <c r="N24" s="207" t="n"/>
@@ -7127,9 +8948,31 @@
     <row r="15" ht="22.5" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="91" t="inlineStr">
         <is>
-          <t>1. Process Item System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>System, Subsystem,
 Part Element or
 Name of Process</t>
+          </r>
         </is>
       </c>
       <c r="B15" s="207" t="n"/>
@@ -7148,8 +8991,30 @@
       <c r="F15" s="207" t="n"/>
       <c r="G15" s="102" t="inlineStr">
         <is>
-          <t>1. Function of the Process Item Function of System, Subsystem,
+          <r>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Function of the Process Item </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t>Function of System, Subsystem,
 Part Element or Process</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="207" t="n"/>
@@ -7370,37 +9235,294 @@
       <c r="B18" s="207" t="n"/>
       <c r="C18" s="218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation No: 
-Stage: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Operation No</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Stage:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> 
 LH / RH RADIATOR SIDE SEAL FITMENT
 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="207" t="n"/>
       <c r="E18" s="219" t="inlineStr">
         <is>
-          <t>1 Man - Operator
-2.Machine-  
+          <r>
+            <t xml:space="preserve">1 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Man </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- Operator
+2.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-  
 Battery tool
-3.Material (Indirect) - PPE's
-4.Method-
+3.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Material (Indirect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> - PPE's
+4.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Method</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-
 Screw &amp; pushpin fitment
-5.Mother Nature
-(Environment)-NA
-6.Measurement- NA</t>
+5.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Mother Nature
+(Environment)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>-NA
+6.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Measurement</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>- NA</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="207" t="n"/>
       <c r="G18" s="220" t="inlineStr">
         <is>
-          <t>Your Plant :
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Correct installation and positioning of the side seal during radiator assembly.
 2. Maintain seal integrity (no cuts, twists or misalignment)
-Ship to Plant : 
-End User : 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> 
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">End User </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Maintain system pressure under operating temperature and vibration
 2. Accommodate thermal expansion between radiator components
 3. Seal the joint between the radiator core and side tank to prevent coolant leakage</t>
+          </r>
         </is>
       </c>
       <c r="H18" s="207" t="n"/>
@@ -7412,30 +9534,183 @@
       <c r="J18" s="207" t="n"/>
       <c r="K18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Man: 
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Man: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. GET THE SIDE SEAL FROM STORAGE BIN
 2. ALIGN THE SIDE SEAL WITH THE BIW AND THEN TIGHT WITH BOLT AND PUSHPIN
-2. Machine:
-Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">2. Machine:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Proper torquing with 6NM
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 3. Material (Indirect) :
-Hand Gloves, Apron
-4. Method:
-1. Take side seal from storage bin
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Hand Gloves, Apron
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">4. Method:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">1. Take side seal from storage bin
 2. Align side seal with BIW and tight with bolt and pushpin
 </t>
+          </r>
         </is>
       </c>
       <c r="L18" s="207" t="n"/>
       <c r="M18" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Wrong part installed or mixed material
 2. FURTHER OPERATION NOT POSSIBLE
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Vehicle overheating
 2. Coolant seepage or visible leak
 3. Customer dissatisfaction</t>
+          </r>
         </is>
       </c>
       <c r="N18" s="207" t="n"/>
@@ -7544,15 +9819,81 @@
       <c r="L20" s="210" t="n"/>
       <c r="M20" s="224" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Cut, torn, pinched, or cracked seal
 2. Seal under-compressed or over-compressed
 3. Rework time required high and further fitment not possible 
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Ship to Plant : </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Reduced cooling efficiency
 2. Engine overheating
 3. Safety risk if overheating occurs during driving</t>
+          </r>
         </is>
       </c>
       <c r="N20" s="207" t="n"/>
@@ -7821,14 +10162,101 @@
       <c r="L25" s="210" t="n"/>
       <c r="M25" s="161" t="inlineStr">
         <is>
-          <t>Your Plant:
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Your Plant:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. DAMAGE OF THREADS / RATTLING DUE TO JOINT LOOSE
 2. Mounting Bolt under-torqued or over-torqued
-Ship to Plant : Nil
-End User:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Ship to Plant :</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Nil</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <b val="1"/>
+              <color rgb="FFFF0000"/>
+              <sz val="12"/>
+            </rPr>
+            <t>End User:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
 1. Customer dissatisfaction due to coolant leak
 2. Coolant dripping under vehicle
 3. Rattling or vibration noise during driving</t>
+          </r>
         </is>
       </c>
       <c r="N25" s="207" t="n"/>
